--- a/docs/sdlc/30_implementation/WS2D-MD-001_モジュール・クラス一覧.xlsx
+++ b/docs/sdlc/30_implementation/WS2D-MD-001_モジュール・クラス一覧.xlsx
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr"/>
       <c r="E171" s="2" t="n">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="F171" s="2" t="n">
         <v>0</v>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>2</v>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F192" s="2" t="n">
         <v>1</v>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>web.routes, web.validation</t>
+          <t>web.validation</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr"/>
       <c r="E222" s="2" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="F222" s="2" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F224" s="2" t="n">
         <v>1</v>
@@ -7093,11 +7093,7 @@
       <c r="G224" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="H224" s="2" t="inlineStr">
-        <is>
-          <t>web.routes</t>
-        </is>
-      </c>
+      <c r="H224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">

--- a/docs/sdlc/30_implementation/WS2D-MD-001_モジュール・クラス一覧.xlsx
+++ b/docs/sdlc/30_implementation/WS2D-MD-001_モジュール・クラス一覧.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クラス一覧" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'モジュール一覧'!$A$1:$H$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'モジュール一覧'!$A$1:$H$239</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'クラス一覧'!$A$1:$F$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr"/>
       <c r="E160" s="2" t="n">
-        <v>1725</v>
+        <v>610</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr"/>
       <c r="E187" s="2" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>1</v>
@@ -6003,7 +6003,11 @@
       <c r="G187" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>web.config</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -6011,7 +6015,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>web/services/auto_run_preview.py</t>
+          <t>web/services/auto_run_pipeline.py</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -6021,19 +6025,23 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>AutoRun承認前プレビューの読み取りモデル。</t>
+          <t>AutoRun パイプライン本体（実行フェーズ群）。</t>
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>52</v>
+        <v>1168</v>
       </c>
       <c r="F188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H188" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>web.config, web.validation</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -6041,7 +6049,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>web/services/cli_runner.py</t>
+          <t>web/services/auto_run_preview.py</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -6051,23 +6059,19 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>CLI モード（画面なし）から本体機能を実行するための Flask 非依存ランナー。</t>
+          <t>AutoRun承認前プレビューの読み取りモデル。</t>
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>313</v>
+        <v>52</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>web.routes</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -6075,7 +6079,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>web/services/comparison_workspace.py</t>
+          <t>web/services/cli_runner.py</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -6085,17 +6089,17 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>現新比較ワークスペース用のデータ整形（P2-2 第2弾）。</t>
+          <t>CLI モード（画面なし）から本体機能を実行するための Flask 非依存ランナー。</t>
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>236</v>
+        <v>308</v>
       </c>
       <c r="F190" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G190" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
     </row>
@@ -6105,7 +6109,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>web/services/condition_run_status.py</t>
+          <t>web/services/comparison_workspace.py</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -6115,11 +6119,11 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>画面別設計の条件に、テスト実行結果を突き合わせる（P2-5）。</t>
+          <t>現新比較ワークスペース用のデータ整形（P2-2 第2弾）。</t>
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="F191" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6139,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>web/services/document_autorun.py</t>
+          <t>web/services/condition_run_status.py</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -6145,23 +6149,19 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>AutoRun文書駆動モードの設定検証と成果物生成。</t>
+          <t>画面別設計の条件に、テスト実行結果を突き合わせる（P2-5）。</t>
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>220</v>
+        <v>84</v>
       </c>
       <c r="F192" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>web.validation</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>web/services/drift_summary.py</t>
+          <t>web/services/document_autorun.py</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -6179,19 +6179,23 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>通知側で共有する版付きdrift_summary.jsonの安全な読取。</t>
+          <t>AutoRun文書駆動モードの設定検証と成果物生成。</t>
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H193" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>web.validation</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -6199,7 +6203,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>web/services/egress_gateway.py</t>
+          <t>web/services/drift_summary.py</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -6209,14 +6213,14 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>K1 送信ゲートウェイ — 全ての外向き通信の唯一の出口。</t>
+          <t>通知側で共有する版付きdrift_summary.jsonの安全な読取。</t>
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>279</v>
+        <v>30</v>
       </c>
       <c r="F194" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G194" s="2" t="n">
         <v>3</v>
@@ -6229,7 +6233,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>web/services/evidence_pack_service.py</t>
+          <t>web/services/egress_gateway.py</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -6239,17 +6243,17 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>AutoRun の実行結果から証跡パックを生成する配線層。</t>
+          <t>K1 送信ゲートウェイ — 全ての外向き通信の唯一の出口。</t>
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>128</v>
+        <v>279</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G195" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H195" s="2" t="inlineStr"/>
     </row>
@@ -6259,7 +6263,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>web/services/export_xlsx.py</t>
+          <t>web/services/evidence_pack_service.py</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -6269,17 +6273,17 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>テスト仕様書一式を 1 つの Excel ブックにまとめる（P2-3）。</t>
+          <t>AutoRun の実行結果から証跡パックを生成する配線層。</t>
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>246</v>
+        <v>128</v>
       </c>
       <c r="F196" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
     </row>
@@ -6289,7 +6293,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>web/services/failure_classifier.py</t>
+          <t>web/services/export_xlsx.py</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -6297,15 +6301,19 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr"/>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>テスト仕様書一式を 1 つの Excel ブックにまとめる（P2-3）。</t>
+        </is>
+      </c>
       <c r="E197" s="2" t="n">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="F197" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G197" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
     </row>
@@ -6315,7 +6323,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>web/services/failure_hypothesis.py</t>
+          <t>web/services/failure_classifier.py</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -6323,19 +6331,15 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>L3 原因特定 — 失敗の仮説を立て、検証して原因を絞り込む。</t>
-        </is>
-      </c>
+      <c r="D198" s="2" t="inlineStr"/>
       <c r="E198" s="2" t="n">
-        <v>196</v>
+        <v>269</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G198" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
     </row>
@@ -6345,7 +6349,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>web/services/job_queue.py</t>
+          <t>web/services/failure_hypothesis.py</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -6355,17 +6359,17 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>非同期クロールジョブの管理。</t>
+          <t>L3 原因特定 — 失敗の仮説を立て、検証して原因を絞り込む。</t>
         </is>
       </c>
       <c r="E199" s="2" t="n">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="F199" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G199" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H199" s="2" t="inlineStr"/>
     </row>
@@ -6375,7 +6379,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>web/services/metrics.py</t>
+          <t>web/services/job_queue.py</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -6385,17 +6389,17 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Prometheus 形式のメトリクスと、その計測点。</t>
+          <t>非同期クロールジョブの管理。</t>
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>149</v>
+        <v>222</v>
       </c>
       <c r="F200" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G200" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H200" s="2" t="inlineStr"/>
     </row>
@@ -6405,7 +6409,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>web/services/mutation_verifier.py</t>
+          <t>web/services/metrics.py</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -6415,17 +6419,17 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>AutoRun 自己検証: 生成したテストが実際に欠陥検出能力を持つかを、</t>
+          <t>Prometheus 形式のメトリクスと、その計測点。</t>
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>198</v>
+        <v>149</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H201" s="2" t="inlineStr"/>
     </row>
@@ -6435,7 +6439,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>web/services/nonfunctional_judge.py</t>
+          <t>web/services/mutation_verifier.py</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -6445,17 +6449,17 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>L4 非機能の合否判定 — 既存の観測データを判定へ接続する。</t>
+          <t>AutoRun 自己検証: 生成したテストが実際に欠陥検出能力を持つかを、</t>
         </is>
       </c>
       <c r="E202" s="2" t="n">
-        <v>288</v>
+        <v>198</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G202" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H202" s="2" t="inlineStr"/>
     </row>
@@ -6465,7 +6469,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>web/services/notifier.py</t>
+          <t>web/services/nonfunctional_judge.py</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -6473,15 +6477,19 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr"/>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>L4 非機能の合否判定 — 既存の観測データを判定へ接続する。</t>
+        </is>
+      </c>
       <c r="E203" s="2" t="n">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G203" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H203" s="2" t="inlineStr"/>
     </row>
@@ -6491,7 +6499,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>web/services/observation_coverage.py</t>
+          <t>web/services/notifier.py</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -6499,19 +6507,15 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>L0 観測の完全性 — 「我々は全体を見たか？」</t>
-        </is>
-      </c>
+      <c r="D204" s="2" t="inlineStr"/>
       <c r="E204" s="2" t="n">
-        <v>202</v>
+        <v>297</v>
       </c>
       <c r="F204" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H204" s="2" t="inlineStr"/>
     </row>
@@ -6521,7 +6525,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>web/services/oidc.py</t>
+          <t>web/services/observation_coverage.py</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -6531,17 +6535,17 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>OIDC による SSO（Microsoft Entra ID / Google Workspace 先行）。</t>
+          <t>L0 観測の完全性 — 「我々は全体を見たか？」</t>
         </is>
       </c>
       <c r="E205" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F205" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G205" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H205" s="2" t="inlineStr"/>
     </row>
@@ -6551,7 +6555,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>web/services/openai_qa.py</t>
+          <t>web/services/oidc.py</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -6559,21 +6563,21 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr"/>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>OIDC による SSO（Microsoft Entra ID / Google Workspace 先行）。</t>
+        </is>
+      </c>
       <c r="E206" s="2" t="n">
-        <v>477</v>
+        <v>201</v>
       </c>
       <c r="F206" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G206" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t>web.config, web.env_store</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -6581,7 +6585,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>web/services/openapi_docs.py</t>
+          <t>web/services/openai_qa.py</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -6589,21 +6593,21 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
-        <is>
-          <t>OpenAPI 仕様を人が読めるHTMLへ変換する。</t>
-        </is>
-      </c>
+      <c r="D207" s="2" t="inlineStr"/>
       <c r="E207" s="2" t="n">
-        <v>121</v>
+        <v>477</v>
       </c>
       <c r="F207" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H207" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>web.config, web.env_store</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -6611,7 +6615,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>web/services/openapi_spec.py</t>
+          <t>web/services/openapi_docs.py</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -6621,11 +6625,11 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>登録済みルートから OpenAPI 3.0 ドキュメントを組み立てる。</t>
+          <t>OpenAPI 仕様を人が読めるHTMLへ変換する。</t>
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F208" s="2" t="n">
         <v>0</v>
@@ -6641,7 +6645,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>web/services/playwright_executor.py</t>
+          <t>web/services/openapi_spec.py</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -6649,15 +6653,19 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr"/>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>登録済みルートから OpenAPI 3.0 ドキュメントを組み立てる。</t>
+        </is>
+      </c>
       <c r="E209" s="2" t="n">
-        <v>1057</v>
+        <v>138</v>
       </c>
       <c r="F209" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G209" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H209" s="2" t="inlineStr"/>
     </row>
@@ -6667,7 +6675,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>web/services/qa/__init__.py</t>
+          <t>web/services/playwright_executor.py</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -6677,13 +6685,13 @@
       </c>
       <c r="D210" s="2" t="inlineStr"/>
       <c r="E210" s="2" t="n">
-        <v>1</v>
+        <v>1057</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
     </row>
@@ -6693,7 +6701,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>web/services/qa/advanced_generator.py</t>
+          <t>web/services/qa/__init__.py</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -6703,7 +6711,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr"/>
       <c r="E211" s="2" t="n">
-        <v>448</v>
+        <v>1</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>0</v>
@@ -6719,7 +6727,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>web/services/qa/advanced_html.py</t>
+          <t>web/services/qa/advanced_generator.py</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -6729,7 +6737,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr"/>
       <c r="E212" s="2" t="n">
-        <v>249</v>
+        <v>448</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -6745,7 +6753,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>web/services/qa/doc_generator.py</t>
+          <t>web/services/qa/advanced_html.py</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -6755,7 +6763,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr"/>
       <c r="E213" s="2" t="n">
-        <v>545</v>
+        <v>249</v>
       </c>
       <c r="F213" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6779,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>web/services/qa/helpers.py</t>
+          <t>web/services/qa/doc_generator.py</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -6781,19 +6789,15 @@
       </c>
       <c r="D214" s="2" t="inlineStr"/>
       <c r="E214" s="2" t="n">
-        <v>420</v>
+        <v>545</v>
       </c>
       <c r="F214" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G214" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H214" s="2" t="inlineStr">
-        <is>
-          <t>web.config, web.summary, web.tenancy, web.validation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -6801,7 +6805,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>web/services/qa/markdown_lite.py</t>
+          <t>web/services/qa/helpers.py</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -6809,21 +6813,21 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
-        <is>
-          <t>軽量 Markdown → HTML 変換（依存なし・XSS安全）。</t>
-        </is>
-      </c>
+      <c r="D215" s="2" t="inlineStr"/>
       <c r="E215" s="2" t="n">
-        <v>148</v>
+        <v>420</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H215" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>web.config, web.summary, web.tenancy, web.validation</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -6831,7 +6835,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>web/services/qa/testcase_docs.py</t>
+          <t>web/services/qa/markdown_lite.py</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -6841,17 +6845,17 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>ローレベルテストケース（前提/手順/期待結果）への決定的変換とHTMLレポート生成。</t>
+          <t>軽量 Markdown → HTML 変換（依存なし・XSS安全）。</t>
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F216" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G216" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
     </row>
@@ -6861,7 +6865,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>web/services/retention.py</t>
+          <t>web/services/qa/testcase_docs.py</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -6871,14 +6875,14 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>スナップショット保持ポリシーと安全な世代GC。</t>
+          <t>ローレベルテストケース（前提/手順/期待結果）への決定的変換とHTMLレポート生成。</t>
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G217" s="2" t="n">
         <v>4</v>
@@ -6891,7 +6895,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>web/services/run_store.py</t>
+          <t>web/services/retention.py</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -6901,17 +6905,17 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>実行回ごとの成果物置き場（runs/&lt;run_id&gt;/）。</t>
+          <t>スナップショット保持ポリシーと安全な世代GC。</t>
         </is>
       </c>
       <c r="E218" s="2" t="n">
-        <v>376</v>
+        <v>272</v>
       </c>
       <c r="F218" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G218" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
     </row>
@@ -6921,7 +6925,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>web/services/scheduler.py</t>
+          <t>web/services/run_store.py</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -6931,23 +6935,19 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>スケジュール実行デーモン。</t>
+          <t>実行回ごとの成果物置き場（runs/&lt;run_id&gt;/）。</t>
         </is>
       </c>
       <c r="E219" s="2" t="n">
-        <v>589</v>
+        <v>376</v>
       </c>
       <c r="F219" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G219" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H219" s="2" t="inlineStr">
-        <is>
-          <t>web.config, web.tenancy</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>web/services/screen_test_design.py</t>
+          <t>web/services/scheduler.py</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -6965,19 +6965,23 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>画面別テスト設計 — 1画面で「何を確認するか」を条件として列挙する。</t>
+          <t>スケジュール実行デーモン。</t>
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>407</v>
+        <v>589</v>
       </c>
       <c r="F220" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G220" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H220" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>web.config, web.tenancy</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -6985,7 +6989,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>web/services/spec_ts_generator.py</t>
+          <t>web/services/screen_test_design.py</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -6993,15 +6997,19 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr"/>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>画面別テスト設計 — 1画面で「何を確認するか」を条件として列挙する。</t>
+        </is>
+      </c>
       <c r="E221" s="2" t="n">
-        <v>760</v>
+        <v>407</v>
       </c>
       <c r="F221" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G221" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
     </row>
@@ -7011,7 +7019,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>web/services/test_design_settings.py</t>
+          <t>web/services/spec_ts_generator.py</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -7021,19 +7029,15 @@
       </c>
       <c r="D222" s="2" t="inlineStr"/>
       <c r="E222" s="2" t="n">
-        <v>157</v>
+        <v>760</v>
       </c>
       <c r="F222" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G222" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t>web.config</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -7041,7 +7045,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>web/services/testcase_spec_generator.py</t>
+          <t>web/services/test_design_settings.py</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -7049,21 +7053,21 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
-        <is>
-          <t>テストケース表 → Playwright .spec.ts の変換。</t>
-        </is>
-      </c>
+      <c r="D223" s="2" t="inlineStr"/>
       <c r="E223" s="2" t="n">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="F223" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G223" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>web.config</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -7071,7 +7075,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>web/services/testcase_table_store.py</t>
+          <t>web/services/testcase_spec_generator.py</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -7081,17 +7085,17 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>テストケース表の永続化（生成値・ユーザー編集・編集履歴）。</t>
+          <t>テストケース表 → Playwright .spec.ts の変換。</t>
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>401</v>
+        <v>237</v>
       </c>
       <c r="F224" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G224" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H224" s="2" t="inlineStr"/>
     </row>
@@ -7101,7 +7105,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>web/services/traceability.py</t>
+          <t>web/services/testcase_table_store.py</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -7109,15 +7113,19 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr"/>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>テストケース表の永続化（生成値・ユーザー編集・編集履歴）。</t>
+        </is>
+      </c>
       <c r="E225" s="2" t="n">
-        <v>178</v>
+        <v>401</v>
       </c>
       <c r="F225" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G225" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
     </row>
@@ -7127,7 +7135,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>web/services/untrusted_content.py</t>
+          <t>web/services/traceability.py</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -7135,19 +7143,15 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t>K2/K3 非信頼コンテンツ境界 — 対象サイト由来のデータは全て汚染済みとして扱う。</t>
-        </is>
-      </c>
+      <c r="D226" s="2" t="inlineStr"/>
       <c r="E226" s="2" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F226" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G226" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
     </row>
@@ -7157,7 +7161,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>web/services/usage_tracker.py</t>
+          <t>web/services/untrusted_content.py</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -7167,17 +7171,17 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>利用実績の記録と削減工数（ROI）の集計。</t>
+          <t>K2/K3 非信頼コンテンツ境界 — 対象サイト由来のデータは全て汚染済みとして扱う。</t>
         </is>
       </c>
       <c r="E227" s="2" t="n">
-        <v>549</v>
+        <v>173</v>
       </c>
       <c r="F227" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G227" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
     </row>
@@ -7187,7 +7191,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>web/services/viewpoint_blueprints.py</t>
+          <t>web/services/usage_tracker.py</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -7197,23 +7201,19 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>観点定義と領域プロファイルから、領域別の観点を生成する。</t>
+          <t>利用実績の記録と削減工数（ROI）の集計。</t>
         </is>
       </c>
       <c r="E228" s="2" t="n">
-        <v>324</v>
+        <v>549</v>
       </c>
       <c r="F228" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G228" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t>web.config</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="H228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>web/services/viewpoint_proposals.py</t>
+          <t>web/services/viewpoint_blueprints.py</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -7229,19 +7229,23 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr"/>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>観点定義と領域プロファイルから、領域別の観点を生成する。</t>
+        </is>
+      </c>
       <c r="E229" s="2" t="n">
-        <v>139</v>
+        <v>324</v>
       </c>
       <c r="F229" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G229" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>web.config, web.env_store</t>
+          <t>web.config</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7255,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>web/services/viewpoint_sources.py</t>
+          <t>web/services/viewpoint_proposals.py</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -7259,21 +7263,21 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>観点の根拠（規格・ガイドライン）を出典へ解決する。</t>
-        </is>
-      </c>
+      <c r="D230" s="2" t="inlineStr"/>
       <c r="E230" s="2" t="n">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="F230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G230" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H230" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>web.config, web.env_store</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -7281,7 +7285,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>web/services/viewpoint_store.py</t>
+          <t>web/services/viewpoint_sources.py</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -7289,21 +7293,21 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr"/>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>観点の根拠（規格・ガイドライン）を出典へ解決する。</t>
+        </is>
+      </c>
       <c r="E231" s="2" t="n">
-        <v>943</v>
+        <v>77</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G231" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H231" s="2" t="inlineStr">
-        <is>
-          <t>web.config, web.tenancy</t>
-        </is>
-      </c>
+      <c r="H231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -7311,7 +7315,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>web/services/viewpoint_store_operations.py</t>
+          <t>web/services/viewpoint_store.py</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -7321,15 +7325,19 @@
       </c>
       <c r="D232" s="2" t="inlineStr"/>
       <c r="E232" s="2" t="n">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="F232" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H232" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>web.config, web.tenancy</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -7337,7 +7345,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>web/services/viewpoint_templates.py</t>
+          <t>web/services/viewpoint_store_operations.py</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -7347,19 +7355,15 @@
       </c>
       <c r="D233" s="2" t="inlineStr"/>
       <c r="E233" s="2" t="n">
-        <v>261</v>
+        <v>955</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G233" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H233" s="2" t="inlineStr">
-        <is>
-          <t>web.config</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -7367,7 +7371,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>web/services/visual_complexity.py</t>
+          <t>web/services/viewpoint_templates.py</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -7375,21 +7379,21 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
-        <is>
-          <t>スクリーンショットから視覚的複雑性と色の豊かさを算出する。</t>
-        </is>
-      </c>
+      <c r="D234" s="2" t="inlineStr"/>
       <c r="E234" s="2" t="n">
-        <v>113</v>
+        <v>261</v>
       </c>
       <c r="F234" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H234" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>web.config</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -7397,7 +7401,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>web/summary.py</t>
+          <t>web/services/visual_complexity.py</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -7405,21 +7409,21 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr"/>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>スクリーンショットから視覚的複雑性と色の豊かさを算出する。</t>
+        </is>
+      </c>
       <c r="E235" s="2" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="F235" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G235" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H235" s="2" t="inlineStr">
-        <is>
-          <t>web.config</t>
-        </is>
-      </c>
+      <c r="H235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -7427,7 +7431,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>web/tenancy.py</t>
+          <t>web/summary.py</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -7435,21 +7439,21 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
-        <is>
-          <t>テナントコンテキストとデータ分離のヘルパー。</t>
-        </is>
-      </c>
+      <c r="D236" s="2" t="inlineStr"/>
       <c r="E236" s="2" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F236" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G236" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H236" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>web.config</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -7457,7 +7461,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>web/types.py</t>
+          <t>web/tenancy.py</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -7467,17 +7471,17 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>プロジェクト全体で共有する TypedDict 定義。</t>
+          <t>テナントコンテキストとデータ分離のヘルパー。</t>
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
     </row>
@@ -7487,32 +7491,62 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
+          <t>web/types.py</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>プロジェクト全体で共有する TypedDict 定義。</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
           <t>web/validation.py</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr"/>
-      <c r="E238" s="2" t="n">
+      <c r="D239" s="2" t="inlineStr"/>
+      <c r="E239" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="F238" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="F239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>web.config, web.tenancy</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H238"/>
+  <autoFilter ref="A1:H239"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
